--- a/data/xlsx/dte--plumbing-and-pipe-fitting.xlsx
+++ b/data/xlsx/dte--plumbing-and-pipe-fitting.xlsx
@@ -647,7 +647,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -669,7 +671,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -691,7 +695,9 @@
       <c r="C18" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -713,7 +719,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -735,7 +743,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -757,7 +767,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -779,7 +791,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -801,7 +815,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -823,7 +839,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -845,7 +863,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -867,7 +887,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -889,7 +911,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -911,7 +935,9 @@
       <c r="C28" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -933,7 +959,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>8</v>
       </c>
@@ -955,7 +983,9 @@
       <c r="C30" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -977,7 +1007,9 @@
       <c r="C31" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -999,7 +1031,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -1021,7 +1055,9 @@
       <c r="C33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -1043,7 +1079,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>8</v>
       </c>
@@ -1065,7 +1103,9 @@
       <c r="C35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>7</v>
       </c>
@@ -1087,7 +1127,9 @@
       <c r="C36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>5</v>
       </c>
@@ -1109,7 +1151,9 @@
       <c r="C37" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -1131,7 +1175,9 @@
       <c r="C38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>5</v>
       </c>

--- a/data/xlsx/dte--plumbing-and-pipe-fitting.xlsx
+++ b/data/xlsx/dte--plumbing-and-pipe-fitting.xlsx
@@ -771,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -843,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F35" s="9">
         <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F37" s="9">
         <f>IFERROR(MIN(C37,D37)*E37/C37,0)</f>
